--- a/dist/time_tracker_2026-05.xlsx
+++ b/dist/time_tracker_2026-05.xlsx
@@ -428,16 +428,16 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -597,7 +597,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-15 10:58:48</t>
+          <t>2026-04-15 14:37:34</t>
         </is>
       </c>
     </row>
